--- a/data/trans_orig/Predimed-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Predimed-Provincia-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de adherencia a la dieta mediterránea (Predimed)</t>
+          <t>Puntuación media de la escala de adherencia a la dieta mediterránea (Predimed) (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,39</t>
+          <t>7,05; 7,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,34</t>
+          <t>7,07; 7,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,33</t>
+          <t>7,12; 7,33</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 5,78</t>
+          <t>5,23; 5,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,56; 5,91</t>
+          <t>5,57; 5,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 5,78</t>
+          <t>5,46; 5,79</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 7,64</t>
+          <t>7,22; 7,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,46; 7,78</t>
+          <t>7,49; 7,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,67</t>
+          <t>7,39; 7,66</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 8,02</t>
+          <t>7,26; 8,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 8,16</t>
+          <t>6,91; 8,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,99</t>
+          <t>7,1; 8,02</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 7,21</t>
+          <t>6,58; 7,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,68</t>
+          <t>7,22; 7,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 7,39</t>
+          <t>7,02; 7,38</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 7,03</t>
+          <t>6,68; 7,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,35; 6,63</t>
+          <t>6,36; 6,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,56; 6,78</t>
+          <t>6,55; 6,78</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,48</t>
+          <t>6,96; 7,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,77</t>
+          <t>7,23; 7,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,61</t>
+          <t>7,21; 7,62</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,25</t>
+          <t>4,55; 6,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,4; 4,73</t>
+          <t>4,41; 4,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,54; 5,76</t>
+          <t>4,54; 5,83</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,45; 6,85</t>
+          <t>6,44; 6,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,42; 6,67</t>
+          <t>6,42; 6,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Predimed-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Predimed-Provincia-trans_orig.xlsx
@@ -553,12 +553,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>7,11</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>7,17</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,39</t>
+          <t>7,07; 7,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,33</t>
+          <t>6,95; 7,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,33</t>
+          <t>7,07; 7,25</t>
         </is>
       </c>
     </row>
@@ -598,12 +598,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>5,5</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 5,75</t>
+          <t>5,28; 5,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 5,91</t>
+          <t>5,59; 5,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 5,79</t>
+          <t>5,48; 5,78</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,43</t>
+          <t>7,4</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,6</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,53</t>
+          <t>7,51</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 7,66</t>
+          <t>7,19; 7,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 7,78</t>
+          <t>7,44; 7,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,66</t>
+          <t>7,38; 7,65</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,63</t>
+          <t>7,8</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,74</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 8,0</t>
+          <t>7,41; 8,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 8,14</t>
+          <t>7,44; 7,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,02</t>
+          <t>7,51; 7,95</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>6,83</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,45</t>
+          <t>7,38</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>7,12</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 7,16</t>
+          <t>6,55; 7,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 7,67</t>
+          <t>7,12; 7,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 7,38</t>
+          <t>6,95; 7,31</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6,85</t>
+          <t>6,83</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,48</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>6,66</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,68; 7,03</t>
+          <t>6,65; 6,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,36; 6,62</t>
+          <t>6,36; 6,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>7,3</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,46</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,38</t>
+          <t>7,28</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,48</t>
+          <t>7,1; 7,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,23; 7,77</t>
+          <t>7,09; 7,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,62</t>
+          <t>7,16; 7,41</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>4,53</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>4,53</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,09</t>
+          <t>4,39; 4,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,41; 4,72</t>
+          <t>4,38; 4,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,54; 5,83</t>
+          <t>4,43; 4,64</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6,44</t>
+          <t>6,37</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>6,4</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,34; 6,57</t>
+          <t>6,28; 6,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,44; 6,88</t>
+          <t>6,35; 6,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,42; 6,68</t>
+          <t>6,33; 6,45</t>
         </is>
       </c>
     </row>
